--- a/data/oregon/intermediate/site_key_final.xlsx
+++ b/data/oregon/intermediate/site_key_final.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/wc_biotoxin_depuration/data/oregon/intermediate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FDD0DD32-99FC-6041-A423-7AEDF5CEA528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0149CFA9-BA31-F04F-862A-CEE613C20A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2000" yWindow="500" windowWidth="30840" windowHeight="20180" xr2:uid="{0E5AD23D-6504-6D42-B7A3-7A679EC1D939}"/>
   </bookViews>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">site_key_temp!$A$1:$B$165</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="216">
   <si>
     <t>site_orig</t>
   </si>
@@ -583,18 +596,6 @@
     <t>Tillamook Bay - Hanging Site</t>
   </si>
   <si>
-    <t>Cape Falcon to Cascade Head</t>
-  </si>
-  <si>
-    <t>Cape Blanco to CA Border</t>
-  </si>
-  <si>
-    <t>Heceta Head to Cape Blanco</t>
-  </si>
-  <si>
-    <t>Cascade Head to Heceta Head</t>
-  </si>
-  <si>
     <t>Cape Falcon @ Oswald West State Park</t>
   </si>
   <si>
@@ -638,13 +639,58 @@
   </si>
   <si>
     <t>50-L: Gold Beach to OR/CA Border</t>
+  </si>
+  <si>
+    <t>coord_source</t>
+  </si>
+  <si>
+    <t>lat_dd</t>
+  </si>
+  <si>
+    <t>long_dd</t>
+  </si>
+  <si>
+    <t>OR Dungeness crab preseason sampling spreadsheet</t>
+  </si>
+  <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t>OR port spreadsheet</t>
+  </si>
+  <si>
+    <t>OR biotoxin sampling site coordinate spreadsheet</t>
+  </si>
+  <si>
+    <t>Cape Perpetua-Neptune State Park</t>
+  </si>
+  <si>
+    <t>Waldport</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>50-K/L: Cape Blanco to OR/CA Border</t>
+  </si>
+  <si>
+    <t>50-B/C: Cape Falcon to Cascade Head</t>
+  </si>
+  <si>
+    <t>50-D/E/F: Cascade Head to Heceta Head</t>
+  </si>
+  <si>
+    <t>50-G/H/I/J: Heceta Head to Cape Blanco</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -785,6 +831,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1130,8 +1182,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1507,1338 +1559,2803 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC5072A-F70B-5642-9A8A-1C18850BBB0E}">
-  <dimension ref="A1:B165"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="C1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2">
+        <v>46</v>
+      </c>
+      <c r="E2">
+        <v>-124.06</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3">
+        <v>46</v>
+      </c>
+      <c r="E3">
+        <v>-124.06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D4">
+        <v>45.55</v>
+      </c>
+      <c r="E4">
+        <v>-124.03333333333333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D5">
+        <v>45.166666666666664</v>
+      </c>
+      <c r="E5">
+        <v>-124.04666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="C6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6">
+        <v>44.9</v>
+      </c>
+      <c r="E6">
+        <v>-124.105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7">
+        <v>44.57</v>
+      </c>
+      <c r="E7">
+        <v>-124.18333333333334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8">
+        <v>44.291666666666664</v>
+      </c>
+      <c r="E8">
+        <v>-124.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D9">
+        <v>43.958333333333336</v>
+      </c>
+      <c r="E9">
+        <v>-124.20833333333333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10">
+        <v>43.608333333333334</v>
+      </c>
+      <c r="E10">
+        <v>-124.255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="C11" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11">
+        <v>43.325000000000003</v>
+      </c>
+      <c r="E11">
+        <v>-124.43833333333333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="C12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D12">
+        <v>42.975000000000001</v>
+      </c>
+      <c r="E12">
+        <v>-124.52333333333333</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="C13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13">
+        <v>42.625</v>
+      </c>
+      <c r="E13">
+        <v>-124.45833333333333</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="D14">
+        <v>42.166666666666664</v>
+      </c>
+      <c r="E14">
+        <v>-124.40166666666667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="B15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15" t="s">
+        <v>205</v>
+      </c>
+      <c r="D15">
+        <v>46.226058999999999</v>
+      </c>
+      <c r="E15">
+        <v>-123.731865</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="C16" t="s">
+        <v>207</v>
+      </c>
+      <c r="D16">
+        <v>44.425933999999998</v>
+      </c>
+      <c r="E16">
+        <v>-124.078045</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+      <c r="C17" t="s">
+        <v>207</v>
+      </c>
+      <c r="D17">
+        <v>44.425933999999998</v>
+      </c>
+      <c r="E17">
+        <v>-124.078045</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+      <c r="C18" t="s">
+        <v>207</v>
+      </c>
+      <c r="D18">
+        <v>44.425933999999998</v>
+      </c>
+      <c r="E18">
+        <v>-124.078045</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+      <c r="C19" t="s">
+        <v>207</v>
+      </c>
+      <c r="D19">
+        <v>45.847546000000001</v>
+      </c>
+      <c r="E19">
+        <v>-123.961873</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+      <c r="C20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D20">
+        <v>46.188889000000003</v>
+      </c>
+      <c r="E20">
+        <v>-123.821111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+      <c r="C21" t="s">
+        <v>205</v>
+      </c>
+      <c r="D21">
+        <v>43.110509999999998</v>
+      </c>
+      <c r="E21">
+        <v>-124.43380500000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+      <c r="C22" t="s">
+        <v>205</v>
+      </c>
+      <c r="D22">
+        <v>43.110509999999998</v>
+      </c>
+      <c r="E22">
+        <v>-124.43380500000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+      <c r="C23" t="s">
+        <v>207</v>
+      </c>
+      <c r="D23">
+        <v>43.342345999999999</v>
+      </c>
+      <c r="E23">
+        <v>-124.359398</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+      <c r="C24" t="s">
+        <v>207</v>
+      </c>
+      <c r="D24">
+        <v>43.342345999999999</v>
+      </c>
+      <c r="E24">
+        <v>-124.359398</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+      <c r="C25" t="s">
+        <v>207</v>
+      </c>
+      <c r="D25">
+        <v>43.342345999999999</v>
+      </c>
+      <c r="E25">
+        <v>-124.359398</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+      <c r="C26" t="s">
+        <v>205</v>
+      </c>
+      <c r="D26">
+        <v>45.519579999999998</v>
+      </c>
+      <c r="E26">
+        <v>-123.94758</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
+      <c r="C27" t="s">
+        <v>205</v>
+      </c>
+      <c r="D27">
+        <v>45.519579999999998</v>
+      </c>
+      <c r="E27">
+        <v>-123.94758</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
+      <c r="C28" t="s">
+        <v>207</v>
+      </c>
+      <c r="D28">
+        <v>44.244584000000003</v>
+      </c>
+      <c r="E28">
+        <v>-124.11383600000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
+      <c r="C29" t="s">
+        <v>207</v>
+      </c>
+      <c r="D29">
+        <v>44.244584000000003</v>
+      </c>
+      <c r="E29">
+        <v>-124.11383600000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
+      <c r="C30" t="s">
+        <v>207</v>
+      </c>
+      <c r="D30">
+        <v>44.244584000000003</v>
+      </c>
+      <c r="E30">
+        <v>-124.11383600000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+      <c r="C31" t="s">
+        <v>205</v>
+      </c>
+      <c r="D31">
+        <v>42.048400999999998</v>
+      </c>
+      <c r="E31">
+        <v>-124.292323</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
+      <c r="C32" t="s">
+        <v>205</v>
+      </c>
+      <c r="D32">
+        <v>45.929105999999997</v>
+      </c>
+      <c r="E32">
+        <v>-123.977814</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
+      <c r="C33" t="s">
+        <v>205</v>
+      </c>
+      <c r="D33">
+        <v>45.929105999999997</v>
+      </c>
+      <c r="E33">
+        <v>-123.977814</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" t="s">
+        <v>212</v>
+      </c>
+      <c r="C34" t="s">
+        <v>211</v>
+      </c>
+      <c r="D34">
+        <v>42.395833333333329</v>
+      </c>
+      <c r="E34">
+        <v>-124.43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>186</v>
+      </c>
+      <c r="C35" t="s">
+        <v>205</v>
+      </c>
+      <c r="D35">
+        <v>45.761260999999998</v>
+      </c>
+      <c r="E35">
+        <v>-123.967082</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>186</v>
+      </c>
+      <c r="C36" t="s">
+        <v>205</v>
+      </c>
+      <c r="D36">
+        <v>45.761260999999998</v>
+      </c>
+      <c r="E36">
+        <v>-123.967082</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" t="s">
+        <v>205</v>
+      </c>
+      <c r="D37">
+        <v>45.761260999999998</v>
+      </c>
+      <c r="E37">
+        <v>-123.967082</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>213</v>
+      </c>
+      <c r="C38" t="s">
+        <v>211</v>
+      </c>
+      <c r="D38">
+        <v>45.358333333333334</v>
+      </c>
+      <c r="E38">
+        <v>-124.03999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" t="s">
+        <v>207</v>
+      </c>
+      <c r="D39">
+        <v>45.473132999999997</v>
+      </c>
+      <c r="E39">
+        <v>-123.970885</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40">
+        <v>45.473132999999997</v>
+      </c>
+      <c r="E40">
+        <v>-123.970885</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" t="s">
+        <v>207</v>
+      </c>
+      <c r="D41">
+        <v>45.473132999999997</v>
+      </c>
+      <c r="E41">
+        <v>-123.970885</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>208</v>
+      </c>
+      <c r="C42" t="s">
+        <v>207</v>
+      </c>
+      <c r="D42">
+        <v>44.265208999999999</v>
+      </c>
+      <c r="E42">
+        <v>-124.10984500000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>208</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D43" s="2">
+        <v>44.265208999999999</v>
+      </c>
+      <c r="E43" s="2">
+        <v>-124.10984500000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>208</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D44" s="2">
+        <v>44.265208999999999</v>
+      </c>
+      <c r="E44" s="2">
+        <v>-124.10984500000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>208</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D45" s="2">
+        <v>44.265208999999999</v>
+      </c>
+      <c r="E45" s="2">
+        <v>-124.10984500000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>214</v>
+      </c>
+      <c r="C46" t="s">
+        <v>211</v>
+      </c>
+      <c r="D46">
+        <v>44.587222222222216</v>
+      </c>
+      <c r="E46">
+        <v>-124.16277777777778</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>170</v>
+      </c>
+      <c r="C47" t="s">
+        <v>205</v>
+      </c>
+      <c r="D47">
+        <v>45.895867000000003</v>
+      </c>
+      <c r="E47">
+        <v>-123.96417599999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>170</v>
+      </c>
+      <c r="C48" t="s">
+        <v>205</v>
+      </c>
+      <c r="D48">
+        <v>45.895867000000003</v>
+      </c>
+      <c r="E48">
+        <v>-123.96417599999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" t="s">
+        <v>207</v>
+      </c>
+      <c r="D49">
+        <v>46.041781999999998</v>
+      </c>
+      <c r="E49">
+        <v>-123.929815</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>171</v>
+      </c>
+      <c r="C50" t="s">
+        <v>207</v>
+      </c>
+      <c r="D50">
+        <v>46.041781999999998</v>
+      </c>
+      <c r="E50">
+        <v>-123.929815</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>171</v>
+      </c>
+      <c r="C51" t="s">
+        <v>207</v>
+      </c>
+      <c r="D51">
+        <v>46.041781999999998</v>
+      </c>
+      <c r="E51">
+        <v>-123.929815</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52" t="s">
+        <v>207</v>
+      </c>
+      <c r="D52">
+        <v>46.030461000000003</v>
+      </c>
+      <c r="E52">
+        <v>-123.929987</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>172</v>
+      </c>
+      <c r="C53" t="s">
+        <v>207</v>
+      </c>
+      <c r="D53">
+        <v>46.030461000000003</v>
+      </c>
+      <c r="E53">
+        <v>-123.929987</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>172</v>
+      </c>
+      <c r="C54" t="s">
+        <v>207</v>
+      </c>
+      <c r="D54">
+        <v>46.030461000000003</v>
+      </c>
+      <c r="E54">
+        <v>-123.929987</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>173</v>
+      </c>
+      <c r="C55" t="s">
+        <v>207</v>
+      </c>
+      <c r="D55">
+        <v>45.992907000000002</v>
+      </c>
+      <c r="E55">
+        <v>-123.93239</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>173</v>
+      </c>
+      <c r="C56" t="s">
+        <v>207</v>
+      </c>
+      <c r="D56">
+        <v>45.992907000000002</v>
+      </c>
+      <c r="E56">
+        <v>-123.93239</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>173</v>
+      </c>
+      <c r="C57" t="s">
+        <v>207</v>
+      </c>
+      <c r="D57">
+        <v>45.992907000000002</v>
+      </c>
+      <c r="E57">
+        <v>-123.93239</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C58" t="s">
+        <v>205</v>
+      </c>
+      <c r="D58">
+        <v>46.229900000000001</v>
+      </c>
+      <c r="E58">
+        <v>-124.025161</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59" t="s">
+        <v>205</v>
+      </c>
+      <c r="D59">
+        <v>46.229900000000001</v>
+      </c>
+      <c r="E59">
+        <v>-124.025161</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>174</v>
+      </c>
+      <c r="C60" t="s">
+        <v>205</v>
+      </c>
+      <c r="D60">
+        <v>46.229900000000001</v>
+      </c>
+      <c r="E60">
+        <v>-124.025161</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" t="s">
+        <v>207</v>
+      </c>
+      <c r="D61">
+        <v>46.098351999999998</v>
+      </c>
+      <c r="E61">
+        <v>-123.941574</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>175</v>
+      </c>
+      <c r="C62" t="s">
+        <v>207</v>
+      </c>
+      <c r="D62">
+        <v>46.098351999999998</v>
+      </c>
+      <c r="E62">
+        <v>-123.941574</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>175</v>
+      </c>
+      <c r="C63" t="s">
+        <v>207</v>
+      </c>
+      <c r="D63">
+        <v>46.098351999999998</v>
+      </c>
+      <c r="E63">
+        <v>-123.941574</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>63</v>
+      </c>
+      <c r="C64" t="s">
+        <v>205</v>
+      </c>
+      <c r="D64">
+        <v>45.992907000000002</v>
+      </c>
+      <c r="E64">
+        <v>-123.93239</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>63</v>
+      </c>
+      <c r="C65" t="s">
+        <v>205</v>
+      </c>
+      <c r="D65">
+        <v>45.992907000000002</v>
+      </c>
+      <c r="E65">
+        <v>-123.93239</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>65</v>
+      </c>
+      <c r="C66" t="s">
+        <v>205</v>
+      </c>
+      <c r="D66">
+        <v>45.992907000000002</v>
+      </c>
+      <c r="E66">
+        <v>-123.93239</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>65</v>
+      </c>
+      <c r="C67" t="s">
+        <v>205</v>
+      </c>
+      <c r="D67">
+        <v>45.992907000000002</v>
+      </c>
+      <c r="E67">
+        <v>-123.93239</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>138</v>
+      </c>
+      <c r="B68" t="s">
+        <v>181</v>
+      </c>
+      <c r="C68" t="s">
+        <v>205</v>
+      </c>
+      <c r="D68">
+        <v>46.231569999999998</v>
+      </c>
+      <c r="E68">
+        <v>-124.02011899999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>139</v>
+      </c>
+      <c r="B69" t="s">
+        <v>181</v>
+      </c>
+      <c r="C69" t="s">
+        <v>205</v>
+      </c>
+      <c r="D69">
+        <v>46.231569999999998</v>
+      </c>
+      <c r="E69">
+        <v>-124.02011899999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" t="s">
+        <v>181</v>
+      </c>
+      <c r="C70" t="s">
+        <v>205</v>
+      </c>
+      <c r="D70">
+        <v>46.231569999999998</v>
+      </c>
+      <c r="E70">
+        <v>-124.02011899999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>67</v>
+      </c>
+      <c r="B71" t="s">
+        <v>67</v>
+      </c>
+      <c r="C71" t="s">
+        <v>206</v>
+      </c>
+      <c r="D71">
+        <v>43.376389000000003</v>
+      </c>
+      <c r="E71">
+        <v>-124.237222</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>68</v>
+      </c>
+      <c r="B72" t="s">
+        <v>68</v>
+      </c>
+      <c r="C72" t="s">
+        <v>205</v>
+      </c>
+      <c r="D72">
+        <v>43.369332</v>
+      </c>
+      <c r="E72">
+        <v>-124.305407</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>69</v>
+      </c>
+      <c r="B73" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" t="s">
+        <v>205</v>
+      </c>
+      <c r="D73">
+        <v>43.369332</v>
+      </c>
+      <c r="E73">
+        <v>-124.305407</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>72</v>
+      </c>
+      <c r="B74" t="s">
+        <v>177</v>
+      </c>
+      <c r="C74" t="s">
+        <v>205</v>
+      </c>
+      <c r="D74">
+        <v>43.359039000000003</v>
+      </c>
+      <c r="E74">
+        <v>-124.34598699999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>73</v>
+      </c>
+      <c r="B75" t="s">
+        <v>177</v>
+      </c>
+      <c r="C75" t="s">
+        <v>205</v>
+      </c>
+      <c r="D75">
+        <v>43.359039000000003</v>
+      </c>
+      <c r="E75">
+        <v>-124.34598699999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>74</v>
+      </c>
+      <c r="B76" t="s">
+        <v>177</v>
+      </c>
+      <c r="C76" t="s">
+        <v>205</v>
+      </c>
+      <c r="D76">
+        <v>43.359039000000003</v>
+      </c>
+      <c r="E76">
+        <v>-124.34598699999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>70</v>
+      </c>
+      <c r="B77" t="s">
+        <v>70</v>
+      </c>
+      <c r="C77" t="s">
+        <v>205</v>
+      </c>
+      <c r="D77">
+        <v>43.385250999999997</v>
+      </c>
+      <c r="E77">
+        <v>-124.197305</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>71</v>
+      </c>
+      <c r="B78" t="s">
+        <v>70</v>
+      </c>
+      <c r="C78" t="s">
+        <v>205</v>
+      </c>
+      <c r="D78">
+        <v>43.385250999999997</v>
+      </c>
+      <c r="E78">
+        <v>-124.197305</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>143</v>
+      </c>
+      <c r="B79" t="s">
+        <v>183</v>
+      </c>
+      <c r="C79" t="s">
+        <v>205</v>
+      </c>
+      <c r="D79">
+        <v>43.314933000000003</v>
+      </c>
+      <c r="E79">
+        <v>-124.32320199999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>144</v>
+      </c>
+      <c r="B80" t="s">
+        <v>183</v>
+      </c>
+      <c r="C80" t="s">
+        <v>205</v>
+      </c>
+      <c r="D80">
+        <v>43.314933000000003</v>
+      </c>
+      <c r="E80">
+        <v>-124.32320199999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>145</v>
+      </c>
+      <c r="B81" t="s">
+        <v>183</v>
+      </c>
+      <c r="C81" t="s">
+        <v>205</v>
+      </c>
+      <c r="D81">
+        <v>43.314933000000003</v>
+      </c>
+      <c r="E81">
+        <v>-124.32320199999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>76</v>
+      </c>
+      <c r="B82" t="s">
+        <v>76</v>
+      </c>
+      <c r="C82" t="s">
+        <v>205</v>
+      </c>
+      <c r="D82">
+        <v>42.913378000000002</v>
+      </c>
+      <c r="E82">
+        <v>-124.50011000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>77</v>
+      </c>
+      <c r="B83" t="s">
+        <v>77</v>
+      </c>
+      <c r="C83" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>78</v>
+      </c>
+      <c r="B84" t="s">
+        <v>77</v>
+      </c>
+      <c r="C84" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>79</v>
+      </c>
+      <c r="B85" t="s">
+        <v>79</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D85" s="2">
+        <v>45.560277999999997</v>
+      </c>
+      <c r="E85" s="2">
+        <v>-123.911389</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>75</v>
+      </c>
+      <c r="B86" t="s">
+        <v>176</v>
+      </c>
+      <c r="C86" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>82</v>
+      </c>
+      <c r="B87" t="s">
+        <v>178</v>
+      </c>
+      <c r="C87" t="s">
+        <v>207</v>
+      </c>
+      <c r="D87">
+        <v>42.302070999999998</v>
+      </c>
+      <c r="E87">
+        <v>-124.413214</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>80</v>
+      </c>
+      <c r="B88" t="s">
+        <v>80</v>
+      </c>
+      <c r="C88" t="s">
+        <v>207</v>
+      </c>
+      <c r="D88">
+        <v>42.302070999999998</v>
+      </c>
+      <c r="E88">
+        <v>-124.413214</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B89" t="s">
+        <v>80</v>
+      </c>
+      <c r="C89" t="s">
+        <v>207</v>
+      </c>
+      <c r="D89">
+        <v>42.302070999999998</v>
+      </c>
+      <c r="E89">
+        <v>-124.413214</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B90" t="s">
+        <v>83</v>
+      </c>
+      <c r="C90" t="s">
+        <v>205</v>
+      </c>
+      <c r="D90">
+        <v>42.063926000000002</v>
+      </c>
+      <c r="E90">
+        <v>-124.305637</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>84</v>
+      </c>
+      <c r="B91" t="s">
+        <v>83</v>
+      </c>
+      <c r="C91" t="s">
+        <v>205</v>
+      </c>
+      <c r="D91">
+        <v>42.063926000000002</v>
+      </c>
+      <c r="E91">
+        <v>-124.305637</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>85</v>
+      </c>
+      <c r="B92" t="s">
+        <v>215</v>
+      </c>
+      <c r="C92" t="s">
+        <v>211</v>
+      </c>
+      <c r="D92">
+        <v>43.466666666666661</v>
+      </c>
+      <c r="E92">
+        <v>-124.35624999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>86</v>
+      </c>
+      <c r="B93" t="s">
+        <v>86</v>
+      </c>
+      <c r="C93" t="s">
+        <v>205</v>
+      </c>
+      <c r="D93">
+        <v>44.077247999999997</v>
+      </c>
+      <c r="E93">
+        <v>-124.127408</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>87</v>
+      </c>
+      <c r="B94" t="s">
+        <v>87</v>
+      </c>
+      <c r="C94" t="s">
+        <v>205</v>
+      </c>
+      <c r="D94">
+        <v>44.058684</v>
+      </c>
+      <c r="E94">
+        <v>-124.129282</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>88</v>
+      </c>
+      <c r="B95" t="s">
+        <v>87</v>
+      </c>
+      <c r="C95" t="s">
+        <v>205</v>
+      </c>
+      <c r="D95">
+        <v>44.058684</v>
+      </c>
+      <c r="E95">
+        <v>-124.129282</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>89</v>
+      </c>
+      <c r="B96" t="s">
+        <v>89</v>
+      </c>
+      <c r="C96" t="s">
+        <v>205</v>
+      </c>
+      <c r="D96">
+        <v>44.652358</v>
+      </c>
+      <c r="E96">
+        <v>-124.06093799999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>90</v>
+      </c>
+      <c r="B97" t="s">
+        <v>89</v>
+      </c>
+      <c r="C97" t="s">
+        <v>205</v>
+      </c>
+      <c r="D97">
+        <v>44.652358</v>
+      </c>
+      <c r="E97">
+        <v>-124.06093799999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>91</v>
+      </c>
+      <c r="B98" t="s">
+        <v>91</v>
+      </c>
+      <c r="C98" t="s">
+        <v>207</v>
+      </c>
+      <c r="D98">
+        <v>44.975667000000001</v>
+      </c>
+      <c r="E98">
+        <v>-124.017448</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>92</v>
+      </c>
+      <c r="B99" t="s">
+        <v>91</v>
+      </c>
+      <c r="C99" t="s">
+        <v>207</v>
+      </c>
+      <c r="D99">
+        <v>44.975667000000001</v>
+      </c>
+      <c r="E99">
+        <v>-124.017448</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>93</v>
+      </c>
+      <c r="B100" t="s">
+        <v>91</v>
+      </c>
+      <c r="C100" t="s">
+        <v>207</v>
+      </c>
+      <c r="D100">
+        <v>44.975667000000001</v>
+      </c>
+      <c r="E100">
+        <v>-124.017448</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>94</v>
+      </c>
+      <c r="B101" t="s">
+        <v>94</v>
+      </c>
+      <c r="C101" t="s">
+        <v>207</v>
+      </c>
+      <c r="D101">
+        <v>45.668779999999998</v>
+      </c>
+      <c r="E101">
+        <v>-123.92539499999999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>95</v>
+      </c>
+      <c r="B102" t="s">
+        <v>94</v>
+      </c>
+      <c r="C102" t="s">
+        <v>207</v>
+      </c>
+      <c r="D102">
+        <v>45.668779999999998</v>
+      </c>
+      <c r="E102">
+        <v>-123.92539499999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>96</v>
+      </c>
+      <c r="B103" t="s">
+        <v>180</v>
+      </c>
+      <c r="C103" t="s">
+        <v>207</v>
+      </c>
+      <c r="D103">
+        <v>45.668779999999998</v>
+      </c>
+      <c r="E103">
+        <v>-123.92539499999999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>97</v>
+      </c>
+      <c r="B104" t="s">
+        <v>180</v>
+      </c>
+      <c r="C104" t="s">
+        <v>207</v>
+      </c>
+      <c r="D104">
+        <v>45.668779999999998</v>
+      </c>
+      <c r="E104">
+        <v>-123.92539499999999</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>98</v>
+      </c>
+      <c r="B105" t="s">
+        <v>98</v>
+      </c>
+      <c r="C105" t="s">
+        <v>207</v>
+      </c>
+      <c r="D105">
+        <v>45.403300999999999</v>
+      </c>
+      <c r="E105">
+        <v>-123.932648</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>99</v>
+      </c>
+      <c r="B106" t="s">
+        <v>98</v>
+      </c>
+      <c r="C106" t="s">
+        <v>207</v>
+      </c>
+      <c r="D106">
+        <v>45.403300999999999</v>
+      </c>
+      <c r="E106">
+        <v>-123.932648</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>100</v>
+      </c>
+      <c r="B107" t="s">
+        <v>100</v>
+      </c>
+      <c r="C107" t="s">
+        <v>207</v>
+      </c>
+      <c r="D107">
+        <v>45.403300999999999</v>
+      </c>
+      <c r="E107">
+        <v>-123.932648</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>101</v>
+      </c>
+      <c r="B108" t="s">
+        <v>100</v>
+      </c>
+      <c r="C108" t="s">
+        <v>207</v>
+      </c>
+      <c r="D108">
+        <v>45.403300999999999</v>
+      </c>
+      <c r="E108">
+        <v>-123.932648</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>102</v>
+      </c>
+      <c r="B109" t="s">
+        <v>102</v>
+      </c>
+      <c r="C109" t="s">
+        <v>205</v>
+      </c>
+      <c r="D109">
+        <v>44.623741000000003</v>
+      </c>
+      <c r="E109">
+        <v>-124.067052</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>105</v>
+      </c>
+      <c r="B110" t="s">
+        <v>105</v>
+      </c>
+      <c r="C110" t="s">
+        <v>205</v>
+      </c>
+      <c r="D110">
+        <v>44.623741000000003</v>
+      </c>
+      <c r="E110">
+        <v>-124.067052</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>106</v>
+      </c>
+      <c r="B111" t="s">
+        <v>105</v>
+      </c>
+      <c r="C111" t="s">
+        <v>205</v>
+      </c>
+      <c r="D111">
+        <v>44.623741000000003</v>
+      </c>
+      <c r="E111">
+        <v>-124.067052</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>103</v>
+      </c>
+      <c r="B112" t="s">
+        <v>107</v>
+      </c>
+      <c r="C112" t="s">
+        <v>207</v>
+      </c>
+      <c r="D112">
+        <v>44.658915999999998</v>
+      </c>
+      <c r="E112">
+        <v>-124.05967699999999</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>104</v>
+      </c>
+      <c r="B113" t="s">
+        <v>107</v>
+      </c>
+      <c r="C113" t="s">
+        <v>207</v>
+      </c>
+      <c r="D113">
+        <v>44.658915999999998</v>
+      </c>
+      <c r="E113">
+        <v>-124.05967699999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>107</v>
+      </c>
+      <c r="B114" t="s">
+        <v>107</v>
+      </c>
+      <c r="C114" t="s">
+        <v>207</v>
+      </c>
+      <c r="D114">
+        <v>44.658915999999998</v>
+      </c>
+      <c r="E114">
+        <v>-124.05967699999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>108</v>
+      </c>
+      <c r="B115" t="s">
+        <v>107</v>
+      </c>
+      <c r="C115" t="s">
+        <v>207</v>
+      </c>
+      <c r="D115">
+        <v>44.658915999999998</v>
+      </c>
+      <c r="E115">
+        <v>-124.05967699999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>109</v>
+      </c>
+      <c r="B116" t="s">
+        <v>107</v>
+      </c>
+      <c r="C116" t="s">
+        <v>207</v>
+      </c>
+      <c r="D116">
+        <v>44.658915999999998</v>
+      </c>
+      <c r="E116">
+        <v>-124.05967699999999</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>110</v>
+      </c>
+      <c r="B117" t="s">
+        <v>110</v>
+      </c>
+      <c r="C117" t="s">
+        <v>205</v>
+      </c>
+      <c r="D117">
+        <v>44.616996999999998</v>
+      </c>
+      <c r="E117">
+        <v>-124.069384</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>111</v>
+      </c>
+      <c r="B118" t="s">
+        <v>110</v>
+      </c>
+      <c r="C118" t="s">
+        <v>205</v>
+      </c>
+      <c r="D118">
+        <v>44.616996999999998</v>
+      </c>
+      <c r="E118">
+        <v>-124.069384</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>112</v>
+      </c>
+      <c r="B119" t="s">
+        <v>110</v>
+      </c>
+      <c r="C119" t="s">
+        <v>205</v>
+      </c>
+      <c r="D119">
+        <v>44.616996999999998</v>
+      </c>
+      <c r="E119">
+        <v>-124.069384</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>116</v>
+      </c>
+      <c r="B120" t="s">
+        <v>110</v>
+      </c>
+      <c r="C120" t="s">
+        <v>205</v>
+      </c>
+      <c r="D120">
+        <v>44.616996999999998</v>
+      </c>
+      <c r="E120">
+        <v>-124.069384</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>117</v>
+      </c>
+      <c r="B121" t="s">
+        <v>110</v>
+      </c>
+      <c r="C121" t="s">
+        <v>205</v>
+      </c>
+      <c r="D121">
+        <v>44.616996999999998</v>
+      </c>
+      <c r="E121">
+        <v>-124.069384</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>113</v>
+      </c>
+      <c r="B122" t="s">
+        <v>113</v>
+      </c>
+      <c r="C122" t="s">
+        <v>205</v>
+      </c>
+      <c r="D122">
+        <v>44.611302000000002</v>
+      </c>
+      <c r="E122">
+        <v>-124.07168900000001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>114</v>
+      </c>
+      <c r="B123" t="s">
+        <v>113</v>
+      </c>
+      <c r="C123" t="s">
+        <v>205</v>
+      </c>
+      <c r="D123">
+        <v>44.611302000000002</v>
+      </c>
+      <c r="E123">
+        <v>-124.07168900000001</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>115</v>
+      </c>
+      <c r="B124" t="s">
+        <v>113</v>
+      </c>
+      <c r="C124" t="s">
+        <v>205</v>
+      </c>
+      <c r="D124">
+        <v>44.611302000000002</v>
+      </c>
+      <c r="E124">
+        <v>-124.07168900000001</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>120</v>
+      </c>
+      <c r="B125" t="s">
+        <v>120</v>
+      </c>
+      <c r="C125" t="s">
+        <v>207</v>
+      </c>
+      <c r="D125">
+        <v>44.520806</v>
+      </c>
+      <c r="E125">
+        <v>-124.07795900000001</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>121</v>
+      </c>
+      <c r="B126" t="s">
+        <v>120</v>
+      </c>
+      <c r="C126" t="s">
+        <v>207</v>
+      </c>
+      <c r="D126">
+        <v>44.520806</v>
+      </c>
+      <c r="E126">
+        <v>-124.07795900000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>122</v>
+      </c>
+      <c r="B127" t="s">
+        <v>120</v>
+      </c>
+      <c r="C127" t="s">
+        <v>207</v>
+      </c>
+      <c r="D127">
+        <v>44.520806</v>
+      </c>
+      <c r="E127">
+        <v>-124.07795900000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>124</v>
+      </c>
+      <c r="B128" t="s">
+        <v>124</v>
+      </c>
+      <c r="C128" t="s">
+        <v>206</v>
+      </c>
+      <c r="D128">
+        <v>42.749721999999998</v>
+      </c>
+      <c r="E128">
+        <v>-124.49805600000001</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>125</v>
+      </c>
+      <c r="B129" t="s">
+        <v>125</v>
+      </c>
+      <c r="C129" t="s">
+        <v>206</v>
+      </c>
+      <c r="D129">
+        <v>42.749721999999998</v>
+      </c>
+      <c r="E129">
+        <v>-124.49805600000001</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>126</v>
+      </c>
+      <c r="B130" t="s">
+        <v>125</v>
+      </c>
+      <c r="C130" t="s">
+        <v>206</v>
+      </c>
+      <c r="D130">
+        <v>42.749721999999998</v>
+      </c>
+      <c r="E130">
+        <v>-124.49805600000001</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>127</v>
+      </c>
+      <c r="B131" t="s">
+        <v>127</v>
+      </c>
+      <c r="C131" t="s">
+        <v>207</v>
+      </c>
+      <c r="D131">
+        <v>44.495648000000003</v>
+      </c>
+      <c r="E131">
+        <v>-124.085126</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>128</v>
+      </c>
+      <c r="B132" t="s">
+        <v>127</v>
+      </c>
+      <c r="C132" t="s">
+        <v>207</v>
+      </c>
+      <c r="D132">
+        <v>44.495648000000003</v>
+      </c>
+      <c r="E132">
+        <v>-124.085126</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>129</v>
+      </c>
+      <c r="B133" t="s">
+        <v>127</v>
+      </c>
+      <c r="C133" t="s">
+        <v>207</v>
+      </c>
+      <c r="D133">
+        <v>44.495648000000003</v>
+      </c>
+      <c r="E133">
+        <v>-124.085126</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>130</v>
+      </c>
+      <c r="B134" t="s">
+        <v>130</v>
+      </c>
+      <c r="C134" t="s">
+        <v>207</v>
+      </c>
+      <c r="D134">
+        <v>44.910420000000002</v>
+      </c>
+      <c r="E134">
+        <v>-124.00697700000001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>131</v>
+      </c>
+      <c r="B135" t="s">
+        <v>130</v>
+      </c>
+      <c r="C135" t="s">
+        <v>207</v>
+      </c>
+      <c r="D135">
+        <v>44.910420000000002</v>
+      </c>
+      <c r="E135">
+        <v>-124.00697700000001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>132</v>
+      </c>
+      <c r="B136" t="s">
+        <v>130</v>
+      </c>
+      <c r="C136" t="s">
+        <v>207</v>
+      </c>
+      <c r="D136">
+        <v>44.910420000000002</v>
+      </c>
+      <c r="E136">
+        <v>-124.00697700000001</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>133</v>
+      </c>
+      <c r="B137" t="s">
+        <v>166</v>
+      </c>
+      <c r="C137" t="s">
+        <v>207</v>
+      </c>
+      <c r="D137">
+        <v>45.847546000000001</v>
+      </c>
+      <c r="E137">
+        <v>-123.961873</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>134</v>
+      </c>
+      <c r="B138" t="s">
+        <v>166</v>
+      </c>
+      <c r="C138" t="s">
+        <v>207</v>
+      </c>
+      <c r="D138">
+        <v>45.847546000000001</v>
+      </c>
+      <c r="E138">
+        <v>-123.961873</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>135</v>
+      </c>
+      <c r="B139" t="s">
+        <v>135</v>
+      </c>
+      <c r="C139" t="s">
+        <v>207</v>
+      </c>
+      <c r="D139">
+        <v>44.018959000000002</v>
+      </c>
+      <c r="E139">
+        <v>-124.143019</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>136</v>
+      </c>
+      <c r="B140" t="s">
+        <v>135</v>
+      </c>
+      <c r="C140" t="s">
+        <v>207</v>
+      </c>
+      <c r="D140">
+        <v>44.018959000000002</v>
+      </c>
+      <c r="E140">
+        <v>-124.143019</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>137</v>
+      </c>
+      <c r="B141" t="s">
+        <v>135</v>
+      </c>
+      <c r="C141" t="s">
+        <v>207</v>
+      </c>
+      <c r="D141">
+        <v>44.018959000000002</v>
+      </c>
+      <c r="E141">
+        <v>-124.143019</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>146</v>
+      </c>
+      <c r="B142" t="s">
+        <v>184</v>
+      </c>
+      <c r="C142" t="s">
+        <v>205</v>
+      </c>
+      <c r="D142">
+        <v>43.746552999999999</v>
+      </c>
+      <c r="E142">
+        <v>-124.182287</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>147</v>
+      </c>
+      <c r="B143" t="s">
+        <v>147</v>
+      </c>
+      <c r="C143" t="s">
+        <v>207</v>
+      </c>
+      <c r="D143">
+        <v>45.520406000000001</v>
+      </c>
+      <c r="E143">
+        <v>-123.94228200000001</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>148</v>
+      </c>
+      <c r="B144" t="s">
+        <v>147</v>
+      </c>
+      <c r="C144" t="s">
+        <v>207</v>
+      </c>
+      <c r="D144">
+        <v>45.520406000000001</v>
+      </c>
+      <c r="E144">
+        <v>-123.94228200000001</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>149</v>
+      </c>
+      <c r="B145" t="s">
+        <v>185</v>
+      </c>
+      <c r="C145" t="s">
+        <v>207</v>
+      </c>
+      <c r="D145">
+        <v>45.520406000000001</v>
+      </c>
+      <c r="E145">
+        <v>-123.94228200000001</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>150</v>
+      </c>
+      <c r="B146" t="s">
+        <v>185</v>
+      </c>
+      <c r="C146" t="s">
+        <v>207</v>
+      </c>
+      <c r="D146">
+        <v>45.520406000000001</v>
+      </c>
+      <c r="E146">
+        <v>-123.94228200000001</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>151</v>
+      </c>
+      <c r="B147" t="s">
+        <v>151</v>
+      </c>
+      <c r="C147" t="s">
+        <v>205</v>
+      </c>
+      <c r="D147">
+        <v>45.403894999999999</v>
+      </c>
+      <c r="E147">
+        <v>-123.96115</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>152</v>
+      </c>
+      <c r="B148" t="s">
+        <v>151</v>
+      </c>
+      <c r="C148" t="s">
+        <v>205</v>
+      </c>
+      <c r="D148">
+        <v>45.403894999999999</v>
+      </c>
+      <c r="E148">
+        <v>-123.96115</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>153</v>
+      </c>
+      <c r="B149" t="s">
+        <v>153</v>
+      </c>
+      <c r="C149" t="s">
+        <v>207</v>
+      </c>
+      <c r="D149">
+        <v>43.665388</v>
+      </c>
+      <c r="E149">
+        <v>-124.209323</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>118</v>
+      </c>
+      <c r="B150" t="s">
+        <v>179</v>
+      </c>
+      <c r="C150" t="s">
+        <v>205</v>
+      </c>
+      <c r="D150">
+        <v>43.670886000000003</v>
+      </c>
+      <c r="E150">
+        <v>-124.217124</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>119</v>
+      </c>
+      <c r="B151" t="s">
+        <v>179</v>
+      </c>
+      <c r="C151" t="s">
+        <v>205</v>
+      </c>
+      <c r="D151">
+        <v>43.670886000000003</v>
+      </c>
+      <c r="E151">
+        <v>-124.217124</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>141</v>
+      </c>
+      <c r="B152" t="s">
+        <v>182</v>
+      </c>
+      <c r="C152" t="s">
+        <v>205</v>
+      </c>
+      <c r="D152">
+        <v>43.666131999999998</v>
+      </c>
+      <c r="E152">
+        <v>-124.21874099999999</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>142</v>
+      </c>
+      <c r="B153" t="s">
+        <v>182</v>
+      </c>
+      <c r="C153" t="s">
+        <v>205</v>
+      </c>
+      <c r="D153">
+        <v>43.666131999999998</v>
+      </c>
+      <c r="E153">
+        <v>-124.21874099999999</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>154</v>
+      </c>
+      <c r="B154" t="s">
+        <v>154</v>
+      </c>
+      <c r="C154" t="s">
+        <v>205</v>
+      </c>
+      <c r="D154">
+        <v>43.376038999999999</v>
+      </c>
+      <c r="E154">
+        <v>-124.19427</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>155</v>
+      </c>
+      <c r="B155" t="s">
+        <v>155</v>
+      </c>
+      <c r="C155" t="s">
+        <v>205</v>
+      </c>
+      <c r="D155">
+        <v>44.418514999999999</v>
+      </c>
+      <c r="E155">
+        <v>-124.08320999999999</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>156</v>
+      </c>
+      <c r="B156" t="s">
+        <v>155</v>
+      </c>
+      <c r="C156" t="s">
+        <v>205</v>
+      </c>
+      <c r="D156">
+        <v>44.418514999999999</v>
+      </c>
+      <c r="E156">
+        <v>-124.08320999999999</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>157</v>
+      </c>
+      <c r="B157" t="s">
+        <v>209</v>
+      </c>
+      <c r="C157" t="s">
+        <v>206</v>
+      </c>
+      <c r="D157">
+        <v>44.426667000000002</v>
+      </c>
+      <c r="E157">
+        <v>-124.068611</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>158</v>
+      </c>
+      <c r="B158" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A78" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A79" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A80" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A81" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A82" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A83" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A84" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A85" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A90" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A91" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A92" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A93" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A94" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A95" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A96" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A97" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A98" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A99" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A100" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A101" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A102" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A103" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A104" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A105" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A106" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A107" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A108" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A109" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A110" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A111" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A112" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A113" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A114" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A115" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A116" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A117" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A118" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A119" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A120" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A121" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A122" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A123" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A124" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A125" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A126" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A127" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A128" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A129" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A130" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A131" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A132" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A133" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A134" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A135" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A136" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A137" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A138" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A139" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A140" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A141" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A142" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A143" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A144" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A145" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A146" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A147" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A148" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A149" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A150" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A151" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A152" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A153" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A154" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A155" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A156" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A157" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A158" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A159" s="2" t="s">
+      <c r="C158" t="s">
+        <v>207</v>
+      </c>
+      <c r="D158">
+        <v>43.212558000000001</v>
+      </c>
+      <c r="E158">
+        <v>-124.395618</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
         <v>159</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A160" s="2" t="s">
+      <c r="B159" t="s">
+        <v>187</v>
+      </c>
+      <c r="C159" t="s">
+        <v>207</v>
+      </c>
+      <c r="D159">
+        <v>43.212558000000001</v>
+      </c>
+      <c r="E159">
+        <v>-124.395618</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
         <v>160</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A161" s="2" t="s">
+      <c r="B160" t="s">
+        <v>187</v>
+      </c>
+      <c r="C160" t="s">
+        <v>207</v>
+      </c>
+      <c r="D160">
+        <v>43.212558000000001</v>
+      </c>
+      <c r="E160">
+        <v>-124.395618</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
         <v>161</v>
       </c>
-      <c r="B161" s="2" t="s">
+      <c r="B161" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A162" s="2" t="s">
+      <c r="C161" t="s">
+        <v>207</v>
+      </c>
+      <c r="D161">
+        <v>44.322896</v>
+      </c>
+      <c r="E161">
+        <v>-124.106627</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
         <v>162</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="B162" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A163" s="2" t="s">
+      <c r="C162" t="s">
+        <v>207</v>
+      </c>
+      <c r="D162">
+        <v>44.322896</v>
+      </c>
+      <c r="E162">
+        <v>-124.106627</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
         <v>163</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="B163" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A164" s="2" t="s">
+      <c r="C163" t="s">
+        <v>207</v>
+      </c>
+      <c r="D163">
+        <v>44.322896</v>
+      </c>
+      <c r="E163">
+        <v>-124.106627</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
         <v>164</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="B164" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A165" s="2" t="s">
+      <c r="C164" t="s">
+        <v>207</v>
+      </c>
+      <c r="D164">
+        <v>44.579417999999997</v>
+      </c>
+      <c r="E164">
+        <v>-123.993287</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
         <v>165</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="B165" t="s">
         <v>164</v>
       </c>
+      <c r="C165" t="s">
+        <v>207</v>
+      </c>
+      <c r="D165">
+        <v>44.579417999999997</v>
+      </c>
+      <c r="E165">
+        <v>-123.993287</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B165" xr:uid="{9FC5072A-F70B-5642-9A8A-1C18850BBB0E}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B165">
-      <sortCondition ref="B1:B165"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>